--- a/data/processed/mizuno_sentiment.xlsx
+++ b/data/processed/mizuno_sentiment.xlsx
@@ -434,12 +434,12 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Leadership_context_human</t>
+          <t>Leadership_context</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Information_valence_human</t>
+          <t>Information_valence</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">

--- a/data/processed/mizuno_sentiment.xlsx
+++ b/data/processed/mizuno_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z63"/>
+  <dimension ref="A1:AB63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,6 +547,16 @@
           <t>finbert_n_chunks</t>
         </is>
       </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>financial_roberta_score</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>finbert_score</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -649,6 +659,12 @@
       <c r="Z2" t="n">
         <v>1</v>
       </c>
+      <c r="AA2" t="n">
+        <v>0.0005215144046815112</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.3466429281979799</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -751,6 +767,12 @@
       <c r="Z3" t="n">
         <v>1</v>
       </c>
+      <c r="AA3" t="n">
+        <v>-0.2018955769017339</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.1905629765242338</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -853,6 +875,12 @@
       <c r="Z4" t="n">
         <v>1</v>
       </c>
+      <c r="AA4" t="n">
+        <v>-0.8333891332149506</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.4672009348869324</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -955,6 +983,12 @@
       <c r="Z5" t="n">
         <v>1</v>
       </c>
+      <c r="AA5" t="n">
+        <v>0.9951729719468858</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.5816698968410492</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1057,6 +1091,12 @@
       <c r="Z6" t="n">
         <v>1</v>
       </c>
+      <c r="AA6" t="n">
+        <v>0.9955581083195284</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.2335384450852871</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1159,6 +1199,12 @@
       <c r="Z7" t="n">
         <v>1</v>
       </c>
+      <c r="AA7" t="n">
+        <v>0.9937667184130987</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.6714927107095718</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1261,6 +1307,12 @@
       <c r="Z8" t="n">
         <v>1</v>
       </c>
+      <c r="AA8" t="n">
+        <v>0.9976668745512143</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.7790924981236458</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1363,6 +1415,12 @@
       <c r="Z9" t="n">
         <v>1</v>
       </c>
+      <c r="AA9" t="n">
+        <v>0.9951925205532461</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.1529875276610255</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1465,6 +1523,12 @@
       <c r="Z10" t="n">
         <v>1</v>
       </c>
+      <c r="AA10" t="n">
+        <v>0.9947777470515575</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.5576838059350848</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1571,6 +1635,12 @@
       <c r="Z11" t="n">
         <v>1</v>
       </c>
+      <c r="AA11" t="n">
+        <v>0.008608030402683653</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.13657156098634</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1675,6 +1745,12 @@
       <c r="Z12" t="n">
         <v>1</v>
       </c>
+      <c r="AA12" t="n">
+        <v>-8.368320413865149e-05</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-0.00990554504096508</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1777,6 +1853,12 @@
       <c r="Z13" t="n">
         <v>1</v>
       </c>
+      <c r="AA13" t="n">
+        <v>0.997623652627226</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.7880583391524851</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1879,6 +1961,12 @@
       <c r="Z14" t="n">
         <v>1</v>
       </c>
+      <c r="AA14" t="n">
+        <v>-0.9977051428286359</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.01100646704435349</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1981,6 +2069,12 @@
       <c r="Z15" t="n">
         <v>1</v>
       </c>
+      <c r="AA15" t="n">
+        <v>0.3206265244516544</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.1659911964088678</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2083,6 +2177,12 @@
       <c r="Z16" t="n">
         <v>1</v>
       </c>
+      <c r="AA16" t="n">
+        <v>0.9973776321276091</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.1939084492623806</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2185,6 +2285,12 @@
       <c r="Z17" t="n">
         <v>1</v>
       </c>
+      <c r="AA17" t="n">
+        <v>0.9968640871229582</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.2999120000749826</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2295,6 +2401,12 @@
       <c r="Z18" t="n">
         <v>1</v>
       </c>
+      <c r="AA18" t="n">
+        <v>0.9971230798400939</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.7533631464466453</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2397,6 +2509,12 @@
       <c r="Z19" t="n">
         <v>1</v>
       </c>
+      <c r="AA19" t="n">
+        <v>0.9972745084087364</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8689127843827009</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2499,6 +2617,12 @@
       <c r="Z20" t="n">
         <v>1</v>
       </c>
+      <c r="AA20" t="n">
+        <v>0.984399281674996</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.2918097525835037</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2603,6 +2727,12 @@
       <c r="Z21" t="n">
         <v>1</v>
       </c>
+      <c r="AA21" t="n">
+        <v>-8.368320413865149e-05</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>-0.00990554504096508</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2705,6 +2835,12 @@
       <c r="Z22" t="n">
         <v>1</v>
       </c>
+      <c r="AA22" t="n">
+        <v>0.9977732473635115</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8241674643941224</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2807,6 +2943,12 @@
       <c r="Z23" t="n">
         <v>1</v>
       </c>
+      <c r="AA23" t="n">
+        <v>0.009211332013364881</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0.3473790055140853</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2909,6 +3051,12 @@
       <c r="Z24" t="n">
         <v>1</v>
       </c>
+      <c r="AA24" t="n">
+        <v>0.996108597406419</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0.6082662576809525</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3011,6 +3159,12 @@
       <c r="Z25" t="n">
         <v>1</v>
       </c>
+      <c r="AA25" t="n">
+        <v>0.9974879888468422</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0.3024260671809316</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3113,6 +3267,12 @@
       <c r="Z26" t="n">
         <v>1</v>
       </c>
+      <c r="AA26" t="n">
+        <v>0.9973002979531884</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0.7117542279884219</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3215,6 +3375,12 @@
       <c r="Z27" t="n">
         <v>1</v>
       </c>
+      <c r="AA27" t="n">
+        <v>0.002117797499522567</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0.5220341393724084</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3317,6 +3483,12 @@
       <c r="Z28" t="n">
         <v>1</v>
       </c>
+      <c r="AA28" t="n">
+        <v>0.9976526213577017</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0.8733100369572639</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3419,6 +3591,12 @@
       <c r="Z29" t="n">
         <v>1</v>
       </c>
+      <c r="AA29" t="n">
+        <v>0.000757395857363008</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0.8276441274210811</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3523,6 +3701,12 @@
       <c r="Z30" t="n">
         <v>1</v>
       </c>
+      <c r="AA30" t="n">
+        <v>-8.368320413865149e-05</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>-0.00990554504096508</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3625,6 +3809,12 @@
       <c r="Z31" t="n">
         <v>1</v>
       </c>
+      <c r="AA31" t="n">
+        <v>0.9976785719627514</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0.8054702831432223</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3727,6 +3917,12 @@
       <c r="Z32" t="n">
         <v>1</v>
       </c>
+      <c r="AA32" t="n">
+        <v>1.885986421257257e-05</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.005189919844269753</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3829,6 +4025,12 @@
       <c r="Z33" t="n">
         <v>1</v>
       </c>
+      <c r="AA33" t="n">
+        <v>0.007185717346146703</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0.1768578542396426</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3931,6 +4133,12 @@
       <c r="Z34" t="n">
         <v>1</v>
       </c>
+      <c r="AA34" t="n">
+        <v>0.9972730203298852</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0.6269264165312052</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4033,6 +4241,12 @@
       <c r="Z35" t="n">
         <v>1</v>
       </c>
+      <c r="AA35" t="n">
+        <v>0.9974008045974188</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0.9080873420462012</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4135,6 +4349,12 @@
       <c r="Z36" t="n">
         <v>1</v>
       </c>
+      <c r="AA36" t="n">
+        <v>0.2368990778923035</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0.1001627519726753</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4237,6 +4457,12 @@
       <c r="Z37" t="n">
         <v>1</v>
       </c>
+      <c r="AA37" t="n">
+        <v>0.9970370634400751</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0.2901239823549986</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4339,6 +4565,12 @@
       <c r="Z38" t="n">
         <v>1</v>
       </c>
+      <c r="AA38" t="n">
+        <v>0.9977817235630937</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0.8808703697286546</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4441,6 +4673,12 @@
       <c r="Z39" t="n">
         <v>1</v>
       </c>
+      <c r="AA39" t="n">
+        <v>0.9956937118258793</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0.1254622098058462</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4543,6 +4781,12 @@
       <c r="Z40" t="n">
         <v>1</v>
       </c>
+      <c r="AA40" t="n">
+        <v>0.3194417446356965</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0.4833692535758018</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4645,6 +4889,12 @@
       <c r="Z41" t="n">
         <v>1</v>
       </c>
+      <c r="AA41" t="n">
+        <v>0.006171867804368958</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0.09612537175416946</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4747,6 +4997,12 @@
       <c r="Z42" t="n">
         <v>1</v>
       </c>
+      <c r="AA42" t="n">
+        <v>0.3246981054544449</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0.31096450984478</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4851,6 +5107,12 @@
       <c r="Z43" t="n">
         <v>1</v>
       </c>
+      <c r="AA43" t="n">
+        <v>-8.368320413865149e-05</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>-0.00990554504096508</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4953,6 +5215,12 @@
       <c r="Z44" t="n">
         <v>1</v>
       </c>
+      <c r="AA44" t="n">
+        <v>0.9959497319650836</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0.4839903246611357</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5055,6 +5323,12 @@
       <c r="Z45" t="n">
         <v>1</v>
       </c>
+      <c r="AA45" t="n">
+        <v>0.994244202185655</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>0.2356390850618482</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5157,6 +5431,12 @@
       <c r="Z46" t="n">
         <v>1</v>
       </c>
+      <c r="AA46" t="n">
+        <v>0.9920626444218215</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0.2582088187336922</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5259,6 +5539,12 @@
       <c r="Z47" t="n">
         <v>1</v>
       </c>
+      <c r="AA47" t="n">
+        <v>0.9958702955045737</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0.3277837913483381</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5361,6 +5647,12 @@
       <c r="Z48" t="n">
         <v>1</v>
       </c>
+      <c r="AA48" t="n">
+        <v>0.9974995260708965</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0.2187763890251517</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5463,6 +5755,12 @@
       <c r="Z49" t="n">
         <v>1</v>
       </c>
+      <c r="AA49" t="n">
+        <v>4.714795795734972e-05</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>0.1126761138439178</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5573,6 +5871,12 @@
       <c r="Z50" t="n">
         <v>1</v>
       </c>
+      <c r="AA50" t="n">
+        <v>0.9976995479082689</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>0.4633567919954658</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5675,6 +5979,12 @@
       <c r="Z51" t="n">
         <v>1</v>
       </c>
+      <c r="AA51" t="n">
+        <v>0.995873767969897</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>0.1844945959746838</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5777,6 +6087,12 @@
       <c r="Z52" t="n">
         <v>1</v>
       </c>
+      <c r="AA52" t="n">
+        <v>0.7323610470630229</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>0.1534941866993904</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5879,6 +6195,12 @@
       <c r="Z53" t="n">
         <v>1</v>
       </c>
+      <c r="AA53" t="n">
+        <v>0.4648959359910805</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>0.5924997515976429</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5981,6 +6303,12 @@
       <c r="Z54" t="n">
         <v>1</v>
       </c>
+      <c r="AA54" t="n">
+        <v>0.99760973372031</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0.2486648382619023</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -6083,6 +6411,12 @@
       <c r="Z55" t="n">
         <v>1</v>
       </c>
+      <c r="AA55" t="n">
+        <v>0.9954959571186919</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>0.567855111323297</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6185,6 +6519,12 @@
       <c r="Z56" t="n">
         <v>1</v>
       </c>
+      <c r="AA56" t="n">
+        <v>0.9973265521111898</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>0.2234346019104123</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6287,6 +6627,12 @@
       <c r="Z57" t="n">
         <v>1</v>
       </c>
+      <c r="AA57" t="n">
+        <v>0.9975729822181165</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>0.8057449692860246</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6389,6 +6735,12 @@
       <c r="Z58" t="n">
         <v>1</v>
       </c>
+      <c r="AA58" t="n">
+        <v>0.2479909007670358</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>0.2282624468207359</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6491,6 +6843,12 @@
       <c r="Z59" t="n">
         <v>1</v>
       </c>
+      <c r="AA59" t="n">
+        <v>0.05204461590619758</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>0.4930668454617262</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6593,6 +6951,12 @@
       <c r="Z60" t="n">
         <v>1</v>
       </c>
+      <c r="AA60" t="n">
+        <v>0.9550140961655416</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>0.5581930102780461</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6695,6 +7059,12 @@
       <c r="Z61" t="n">
         <v>1</v>
       </c>
+      <c r="AA61" t="n">
+        <v>0.9975309295696206</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>0.2473572613671422</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6797,6 +7167,12 @@
       <c r="Z62" t="n">
         <v>1</v>
       </c>
+      <c r="AA62" t="n">
+        <v>0.9969534632982686</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>0.8147890148684382</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6900,6 +7276,12 @@
       </c>
       <c r="Z63" t="n">
         <v>1</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>-8.368320413865149e-05</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>-0.00990554504096508</v>
       </c>
     </row>
   </sheetData>
